--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_automotive.xlsx
@@ -587,23 +587,26 @@
           <t>Retail (Automotive)</t>
         </is>
       </c>
+      <c r="E2">
+        <v>-0.472</v>
+      </c>
       <c r="G2">
-        <v>-2.585657370517928</v>
+        <v>-1.802935889754344</v>
       </c>
       <c r="H2">
-        <v>-2.585657370517928</v>
+        <v>-1.816956261234272</v>
       </c>
       <c r="I2">
-        <v>-2.888557768924302</v>
+        <v>-0.4779688436189334</v>
       </c>
       <c r="J2">
-        <v>-2.888557768924302</v>
+        <v>-0.4779688436189334</v>
       </c>
       <c r="K2">
-        <v>-380.6</v>
+        <v>-124.999</v>
       </c>
       <c r="L2">
-        <v>-3.032669322709164</v>
+        <v>-0.7489454763331336</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>16.006</v>
+        <v>31.9</v>
       </c>
       <c r="V2">
-        <v>0.01873580709352687</v>
+        <v>0.08294331773270931</v>
       </c>
       <c r="W2">
-        <v>1.465930144788307</v>
+        <v>-0.8022648578811369</v>
       </c>
       <c r="X2">
-        <v>0.1067385306027873</v>
+        <v>0.08488410078038452</v>
       </c>
       <c r="Y2">
-        <v>1.35919161418552</v>
+        <v>-0.8871489586615214</v>
       </c>
       <c r="Z2">
-        <v>0.2412375969275364</v>
+        <v>0.5520640381053189</v>
       </c>
       <c r="AA2">
-        <v>-1.538733798755259</v>
+        <v>-0.1475245813489015</v>
       </c>
       <c r="AB2">
-        <v>0.07920238531812504</v>
+        <v>0.07095345497077019</v>
       </c>
       <c r="AC2">
-        <v>-1.617936184073384</v>
+        <v>-0.2184780363196717</v>
       </c>
       <c r="AD2">
-        <v>242</v>
+        <v>403.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>242</v>
+        <v>403.9</v>
       </c>
       <c r="AG2">
-        <v>225.994</v>
+        <v>372</v>
       </c>
       <c r="AH2">
-        <v>0.2207424974915626</v>
+        <v>0.5122384273937857</v>
       </c>
       <c r="AI2">
-        <v>0.5541561712846348</v>
+        <v>1.078792735042735</v>
       </c>
       <c r="AJ2">
-        <v>0.2091967556979859</v>
+        <v>0.4916732751784299</v>
       </c>
       <c r="AK2">
-        <v>0.5371933043970202</v>
+        <v>1.086131386861314</v>
       </c>
       <c r="AL2">
-        <v>3.91</v>
+        <v>24.102</v>
       </c>
       <c r="AM2">
-        <v>3.91</v>
+        <v>24.102</v>
       </c>
       <c r="AN2">
-        <v>-0.7187407187407188</v>
+        <v>-7.06081848854081</v>
       </c>
       <c r="AO2">
-        <v>-92.71457800511507</v>
+        <v>-3.309808314662683</v>
       </c>
       <c r="AP2">
-        <v>-0.6712028512028512</v>
+        <v>-6.503155428911071</v>
       </c>
       <c r="AQ2">
-        <v>-92.71457800511507</v>
+        <v>-3.309808314662683</v>
       </c>
     </row>
     <row r="3">
@@ -712,8 +715,11 @@
           <t>Retail (Automotive)</t>
         </is>
       </c>
+      <c r="E3">
+        <v>-0.472</v>
+      </c>
       <c r="K3">
-        <v>-26.6</v>
+        <v>0.301</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +728,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,73 +737,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.006</v>
+        <v>1.4</v>
       </c>
       <c r="V3">
-        <v>0.0003896103896103896</v>
+        <v>0.0748663101604278</v>
       </c>
       <c r="W3">
-        <v>-0.1734028683181226</v>
+        <v>0.01433333333333333</v>
       </c>
       <c r="X3">
-        <v>0.1235559868228525</v>
+        <v>0.07149466568881499</v>
       </c>
       <c r="Y3">
-        <v>-0.2969588551409751</v>
+        <v>-0.05716133235548165</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.0002832551482865549</v>
+        <v>-0.0141304347826087</v>
       </c>
       <c r="AB3">
-        <v>0.07640464237631085</v>
+        <v>0.07149466568881499</v>
       </c>
       <c r="AC3">
-        <v>-0.07668789752459741</v>
+        <v>-0.08562510047142369</v>
       </c>
       <c r="AD3">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>20.394</v>
+        <v>-1.4</v>
       </c>
       <c r="AH3">
-        <v>0.5698324022346368</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1493411420204978</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.569760295021512</v>
+        <v>-0.08092485549132947</v>
       </c>
       <c r="AK3">
-        <v>0.1493037761541502</v>
+        <v>-0.0673076923076923</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AN3">
-        <v>1.406896551724138</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>-136.5</v>
       </c>
       <c r="AP3">
-        <v>1.40648275862069</v>
+        <v>-3.526448362720402</v>
+      </c>
+      <c r="AQ3">
+        <v>-136.5</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +829,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-2.701195219123506</v>
+        <v>-1.809826243259437</v>
       </c>
       <c r="H4">
-        <v>-2.701195219123506</v>
+        <v>-1.823846614739365</v>
       </c>
       <c r="I4">
-        <v>-2.887649402390438</v>
+        <v>-0.4763331336129419</v>
       </c>
       <c r="J4">
-        <v>-2.887649402390438</v>
+        <v>-0.4763331336129419</v>
       </c>
       <c r="K4">
-        <v>-354</v>
+        <v>-125.3</v>
       </c>
       <c r="L4">
-        <v>-2.820717131474104</v>
+        <v>-0.7507489514679448</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -856,73 +868,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>16</v>
+        <v>30.5</v>
       </c>
       <c r="V4">
-        <v>0.01907259506496603</v>
+        <v>0.08335610822629134</v>
       </c>
       <c r="W4">
-        <v>3.105263157894737</v>
+        <v>-1.618863049095607</v>
       </c>
       <c r="X4">
-        <v>0.08992107438272207</v>
+        <v>0.09827353587195406</v>
       </c>
       <c r="Y4">
-        <v>3.015342083512015</v>
+        <v>-1.717136584967561</v>
       </c>
       <c r="Z4">
-        <v>1.0656364099516</v>
+        <v>0.5897526501766784</v>
       </c>
       <c r="AA4">
-        <v>-3.077184342362231</v>
+        <v>-0.2809187279151943</v>
       </c>
       <c r="AB4">
-        <v>0.08200012825993921</v>
+        <v>0.07041224425272538</v>
       </c>
       <c r="AC4">
-        <v>-3.15918447062217</v>
+        <v>-0.3513309721679198</v>
       </c>
       <c r="AD4">
-        <v>221.6</v>
+        <v>403.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>221.6</v>
+        <v>403.9</v>
       </c>
       <c r="AG4">
-        <v>205.6</v>
+        <v>373.4</v>
       </c>
       <c r="AH4">
-        <v>0.208958038661009</v>
+        <v>0.5246817355157184</v>
       </c>
       <c r="AI4">
-        <v>0.7384205264911695</v>
+        <v>1.14679159568427</v>
       </c>
       <c r="AJ4">
-        <v>0.1968405935854476</v>
+        <v>0.5050723657513865</v>
       </c>
       <c r="AK4">
-        <v>0.7236888419570573</v>
+        <v>1.16070873484613</v>
       </c>
       <c r="AL4">
-        <v>3.91</v>
+        <v>24.1</v>
       </c>
       <c r="AM4">
-        <v>3.91</v>
+        <v>24.1</v>
       </c>
       <c r="AN4">
-        <v>-0.6309794988610479</v>
+        <v>-7.012152777777777</v>
       </c>
       <c r="AO4">
-        <v>-92.6854219948849</v>
+        <v>-3.298755186721992</v>
       </c>
       <c r="AP4">
-        <v>-0.5854214123006833</v>
+        <v>-6.482638888888888</v>
       </c>
       <c r="AQ4">
-        <v>-92.6854219948849</v>
+        <v>-3.298755186721992</v>
       </c>
     </row>
   </sheetData>
